--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-droit-decision.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/StructureDefinition-tddui-basic-droit-decision.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T19:21:03+00:00</t>
+    <t>2026-03-17T13:04:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
